--- a/output/graficos_nacionales/plot_nacional_serie_i_ingr_mean_m_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_ingr_mean_m_2021.xlsx
@@ -282,7 +282,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 09:15</t>
+    <t xml:space="preserve">2026-10-05 18:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -694,7 +694,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -798,7 +798,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -846,7 +846,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -1118,7 +1118,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1294,7 +1294,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1342,7 +1342,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
